--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_5/231FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_5/231FL_10A.xlsx
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7772,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
